--- a/FASE 1/Evidencias_Grupales/PLANILLA DE EVALUACIÓN FASE 1.xlsx
+++ b/FASE 1/Evidencias_Grupales/PLANILLA DE EVALUACIÓN FASE 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSDD\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE46AFA-CC99-408E-8BF9-39DC6E789259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0570DE9-23B0-4AC3-8849-1D371DF6A401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,9 +108,6 @@
     </r>
   </si>
   <si>
-    <t>Maximiliano Leiva</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -189,9 +186,6 @@
   </si>
   <si>
     <t xml:space="preserve">4.  Argumenta por qué el proyecto es factible de realizarse en el marco de la asignatura. </t>
-  </si>
-  <si>
-    <t>Martin Carriel</t>
   </si>
   <si>
     <t>Justifica por qué el proyecto puede desarrollarse considerado tiempo, materiales y factores externos, y en caso de posibles dificultades plantea como las abordaría.</t>
@@ -390,6 +384,12 @@
   </si>
   <si>
     <t>PUNTAJE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAXIMILIANO ANDRES LEIVA ROZAS </t>
+  </si>
+  <si>
+    <t>MARTIN IGNACIO CARRIEL GALAZ</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="C4" s="14">
         <f>EVALUACION1!$C$24</f>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="C5" s="14">
         <f>EVALUACION1!$C$24</f>
@@ -1462,14 +1462,14 @@
     </row>
     <row r="11" spans="1:11" ht="18.5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A11" s="51" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B11" s="26"/>
       <c r="C11" s="57" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E11" s="59"/>
       <c r="F11" s="59"/>
@@ -1482,23 +1482,23 @@
     <row r="12" spans="1:11" ht="14.5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A12" s="52"/>
       <c r="B12" s="28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C12" s="53"/>
       <c r="D12" s="58" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E12" s="60"/>
       <c r="F12" s="58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G12" s="60"/>
       <c r="H12" s="58" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I12" s="60"/>
       <c r="J12" s="58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K12" s="60"/>
     </row>
@@ -1509,7 +1509,7 @@
         <v>1. Describe brevemente en qué consiste el Proyecto APT, justificando su relevancia para el campo laboral de su carrera.</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D13" s="31"/>
       <c r="E13" s="31"/>
@@ -1545,7 +1545,7 @@
         <v>2. Relaciona el Proyecto APT con las competencias del perfil de egreso de su Plan de Estudio.</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D14" s="31" t="str">
         <f t="shared" si="1"/>
@@ -1587,7 +1587,7 @@
         <v xml:space="preserve">4.  Argumenta por qué el proyecto es factible de realizarse en el marco de la asignatura. </v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D15" s="31"/>
       <c r="E15" s="31"/>
@@ -1623,7 +1623,7 @@
         <v xml:space="preserve">5. Formula objetivos claros, concisos y coherentes con la disciplina y la situación a abordar. </v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
@@ -1659,7 +1659,7 @@
         <v>6. Propone una metodología de trabajo que permite alcanzar los objetivos propuestos y es pertinente con los requerimientos disciplinares.</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
@@ -1695,7 +1695,7 @@
         <v xml:space="preserve">7. Establece un plan de trabajo para su proyecto APT considerando los recursos, duración, facilitadores y obstaculizadores en el desarrollo de las actividades. </v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
@@ -1731,7 +1731,7 @@
         <v>8. Determina evidencias, justificando cómo estas dan cuenta del logro de las actividades del Proyecto APT.</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D19" s="31"/>
       <c r="E19" s="31"/>
@@ -1767,7 +1767,7 @@
         <v xml:space="preserve">9. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D20" s="31" t="str">
         <f t="shared" si="1"/>
@@ -1809,7 +1809,7 @@
         <v>10. Cumple completando el contenido del informe de presentación del proyecto de acuerdo con la plantilla entregada.</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D21" s="31"/>
       <c r="E21" s="31"/>
@@ -1846,7 +1846,7 @@
 acuerdo a los tiempos para su desarrollo</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D22" s="31" t="str">
         <f t="shared" si="1"/>
@@ -1925,14 +1925,14 @@
     <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="54" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C27" s="61" t="str">
         <f>$B$4</f>
-        <v>Maximiliano Leiva</v>
+        <v xml:space="preserve">MAXIMILIANO ANDRES LEIVA ROZAS </v>
       </c>
       <c r="D27" s="62"/>
       <c r="E27" s="62"/>
@@ -1959,13 +1959,13 @@
     <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="52"/>
       <c r="B29" s="26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D29" s="58" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E29" s="59"/>
       <c r="F29" s="59"/>
@@ -1978,23 +1978,23 @@
     <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="52"/>
       <c r="B30" s="45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C30" s="53"/>
       <c r="D30" s="58" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E30" s="60"/>
       <c r="F30" s="58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G30" s="60"/>
       <c r="H30" s="58" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I30" s="60"/>
       <c r="J30" s="58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K30" s="60"/>
     </row>
@@ -2005,7 +2005,7 @@
         <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D31" s="31" t="str">
         <f>IF($C31=CL,"X","")</f>
@@ -2047,7 +2047,7 @@
         <v>11. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D32" s="31"/>
       <c r="E32" s="31"/>
@@ -2083,7 +2083,7 @@
         <v>13. Colaboración y trabajo en equipo *</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D33" s="31" t="str">
         <f>IF($C33=CL,"X","")</f>
@@ -2121,7 +2121,7 @@
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="52"/>
       <c r="B34" s="46" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C34" s="47">
         <f>E34+G34+I34+K34</f>
@@ -2169,14 +2169,14 @@
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="54" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B39" s="55" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C39" s="61" t="str">
         <f>B5</f>
-        <v>Martin Carriel</v>
+        <v>MARTIN IGNACIO CARRIEL GALAZ</v>
       </c>
       <c r="D39" s="62"/>
       <c r="E39" s="62"/>
@@ -2203,13 +2203,13 @@
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="52"/>
       <c r="B41" s="26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D41" s="58" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E41" s="59"/>
       <c r="F41" s="59"/>
@@ -2222,23 +2222,23 @@
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="52"/>
       <c r="B42" s="45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C42" s="53"/>
       <c r="D42" s="58" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E42" s="60"/>
       <c r="F42" s="58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G42" s="60"/>
       <c r="H42" s="58" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I42" s="60"/>
       <c r="J42" s="58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K42" s="60"/>
     </row>
@@ -2249,7 +2249,7 @@
         <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D43" s="31" t="str">
         <f>IF($C43=CL,"X","")</f>
@@ -2291,7 +2291,7 @@
         <v>11. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D44" s="31"/>
       <c r="E44" s="31"/>
@@ -2327,7 +2327,7 @@
         <v>13. Colaboración y trabajo en equipo *</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D45" s="31" t="str">
         <f>IF($C45=CL,"X","")</f>
@@ -2365,7 +2365,7 @@
     <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="52"/>
       <c r="B46" s="46" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C46" s="47">
         <f>E46+G46+I46+K46</f>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="79" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B50" s="78" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="61">
         <f>B6</f>
@@ -2446,13 +2446,13 @@
     <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="52"/>
       <c r="B52" s="26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C52" s="77" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D52" s="58" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E52" s="59"/>
       <c r="F52" s="59"/>
@@ -2465,23 +2465,23 @@
     <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="52"/>
       <c r="B53" s="45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C53" s="53"/>
       <c r="D53" s="58" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E53" s="60"/>
       <c r="F53" s="58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G53" s="60"/>
       <c r="H53" s="58" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I53" s="60"/>
       <c r="J53" s="58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K53" s="60"/>
     </row>
@@ -2492,7 +2492,7 @@
         <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D54" s="31" t="str">
         <f>IF($C54=CL,"X","")</f>
@@ -2534,7 +2534,7 @@
         <v>11. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D55" s="31" t="str">
         <f>IF($C55=CL,"X","")</f>
@@ -2569,7 +2569,7 @@
         <v>13. Colaboración y trabajo en equipo *</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D56" s="31" t="str">
         <f>IF($C56=CL,"X","")</f>
@@ -2607,7 +2607,7 @@
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="52"/>
       <c r="B57" s="46" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C57" s="47">
         <f>E57+G57+I57+K57</f>
@@ -3703,13 +3703,13 @@
         <v>8</v>
       </c>
       <c r="C3" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>11</v>
-      </c>
       <c r="E3" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="68"/>
     </row>
@@ -3727,19 +3727,19 @@
     </row>
     <row r="5" spans="1:6" ht="78" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="C5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="13" t="s">
         <v>18</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>19</v>
       </c>
       <c r="F5" s="15">
         <v>10</v>
@@ -3747,19 +3747,19 @@
     </row>
     <row r="6" spans="1:6" ht="65" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="C6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="E6" s="17" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>24</v>
       </c>
       <c r="F6" s="18">
         <v>5</v>
@@ -3767,19 +3767,19 @@
     </row>
     <row r="7" spans="1:6" ht="94.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="C7" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="E7" s="19" t="s">
         <v>28</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="F7" s="21">
         <v>10</v>
@@ -3787,19 +3787,19 @@
     </row>
     <row r="8" spans="1:6" ht="65" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="C8" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="E8" s="19" t="s">
         <v>33</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>35</v>
       </c>
       <c r="F8" s="21">
         <v>5</v>
@@ -3807,19 +3807,19 @@
     </row>
     <row r="9" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="D9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="E9" s="13" t="s">
         <v>38</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="F9" s="15">
         <v>5</v>
@@ -3827,19 +3827,19 @@
     </row>
     <row r="10" spans="1:6" ht="65" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="D10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="E10" s="13" t="s">
         <v>43</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="F10" s="15">
         <v>10</v>
@@ -3847,19 +3847,19 @@
     </row>
     <row r="11" spans="1:6" ht="65" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="D11" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="E11" s="16" t="s">
         <v>48</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>50</v>
       </c>
       <c r="F11" s="18">
         <v>10</v>
@@ -3867,19 +3867,19 @@
     </row>
     <row r="12" spans="1:6" ht="52" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="D12" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="E12" s="17" t="s">
         <v>53</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>55</v>
       </c>
       <c r="F12" s="24">
         <v>5</v>
@@ -3887,19 +3887,19 @@
     </row>
     <row r="13" spans="1:6" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="D13" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="E13" s="19" t="s">
         <v>58</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>60</v>
       </c>
       <c r="F13" s="25">
         <v>5</v>
@@ -3907,19 +3907,19 @@
     </row>
     <row r="14" spans="1:6" ht="65" x14ac:dyDescent="0.35">
       <c r="A14" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="D14" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="E14" s="19" t="s">
         <v>63</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>65</v>
       </c>
       <c r="F14" s="25">
         <v>5</v>
@@ -3927,19 +3927,19 @@
     </row>
     <row r="15" spans="1:6" ht="65" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="D15" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="E15" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="F15" s="15">
         <v>10</v>
@@ -3947,19 +3947,19 @@
     </row>
     <row r="16" spans="1:6" ht="78" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="D16" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="E16" s="13" t="s">
         <v>74</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>76</v>
       </c>
       <c r="F16" s="15">
         <v>10</v>
@@ -3967,19 +3967,19 @@
     </row>
     <row r="17" spans="1:6" ht="91" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="D17" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="E17" s="13" t="s">
         <v>79</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="F17" s="15">
         <v>10</v>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="18" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="74" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B18" s="71"/>
       <c r="C18" s="71"/>
@@ -7009,10 +7009,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
@@ -9849,7 +9849,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="75" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>1</v>
@@ -9861,21 +9861,21 @@
     <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="76"/>
       <c r="B2" s="35" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B3" s="39">
         <v>4</v>
